--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\UnityBasic_6\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_NRUnityProjects\2DMainProject\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,93 +19,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="39">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
     <x:t>옥수수</x:t>
   </x:si>
   <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
+    <x:t>사과</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
@@ -114,28 +141,13 @@
     <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Gold_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
+    <x:t>Icon/Icon_Item_Apple_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -937,80 +949,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>0</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D3" s="14" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>18</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1019,7 +1031,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1029,19 +1041,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1050,7 +1062,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1060,19 +1072,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>19</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1081,7 +1093,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1090,19 +1102,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1111,7 +1123,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1121,19 +1133,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1142,7 +1154,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1152,19 +1164,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>50</x:v>
@@ -1173,7 +1185,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1182,14 +1194,30 @@
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="4"/>
-      <x:c r="E10" s="4"/>
-      <x:c r="F10" s="4"/>
-      <x:c r="G10" s="4"/>
-      <x:c r="H10" s="4"/>
+      <x:c r="A10" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F10" s="4">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G10" s="4">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H10" s="4" t="s">
+        <x:v>42</x:v>
+      </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21825" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="19410" windowHeight="9945"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,120 +19,180 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="43">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
+  <x:si>
+    <x:t>허름한 나무 지팡이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고목 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법학교에서 본것같은 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
   <x:si>
     <x:t>Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Corn</x:t>
   </x:si>
   <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Apple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과</x:t>
+    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
@@ -141,13 +201,70 @@
     <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
   </x:si>
   <x:si>
+    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Box_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Icon_Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>떡갈나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -949,80 +1066,80 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>35</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>27</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1031,7 +1148,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1041,19 +1158,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1062,7 +1179,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1072,19 +1189,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1093,7 +1210,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1102,19 +1219,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1123,7 +1240,7 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1133,19 +1250,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>29</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1154,7 +1271,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1164,19 +1281,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>50</x:v>
@@ -1185,7 +1302,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1195,19 +1312,19 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="4">
         <x:v>50</x:v>
@@ -1216,7 +1333,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1225,14 +1342,30 @@
       <x:c r="M10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
+      <x:c r="A11" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D11" s="4" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F11" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G11" s="4">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H11" s="4" t="s">
+        <x:v>79</x:v>
+      </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
       <x:c r="K11" s="4"/>
@@ -1240,14 +1373,30 @@
       <x:c r="M11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
-      <x:c r="C12" s="6"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
+      <x:c r="A12" s="6" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D12" s="4" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="F12" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G12" s="4">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H12" s="4" t="s">
+        <x:v>81</x:v>
+      </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
       <x:c r="K12" s="4"/>
@@ -1255,14 +1404,30 @@
       <x:c r="M12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="3"/>
-      <x:c r="C13" s="3"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
+      <x:c r="A13" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B13" s="3" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F13" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G13" s="4">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="H13" s="4" t="s">
+        <x:v>76</x:v>
+      </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
       <x:c r="K13" s="4"/>
@@ -1270,14 +1435,30 @@
       <x:c r="M13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A14" s="1"/>
-      <x:c r="B14" s="1"/>
-      <x:c r="C14" s="1"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
+      <x:c r="A14" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F14" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G14" s="4">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H14" s="4" t="s">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
       <x:c r="K14" s="4"/>
@@ -1285,39 +1466,139 @@
       <x:c r="M14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
-      <x:c r="C15" s="1"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
+      <x:c r="A15" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F15" s="4">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G15" s="4">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H15" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
       <x:c r="K15" s="4"/>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="7"/>
-      <x:c r="B16" s="7"/>
-      <x:c r="C16" s="7"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="8"/>
-      <x:c r="B17" s="8"/>
-      <x:c r="C17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="8"/>
-      <x:c r="B18" s="8"/>
-      <x:c r="C18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A19" s="8"/>
-      <x:c r="B19" s="8"/>
-      <x:c r="C19" s="8"/>
+    <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A16" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F16" s="2">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G16" s="2">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H16" s="2" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A17" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F17" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G17" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H17" s="2" t="s">
+        <x:v>64</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A18" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E18" s="2" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F18" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G18" s="2">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H18" s="2" t="s">
+        <x:v>65</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A19" s="8" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F19" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G19" s="2">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="H19" s="2" t="s">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A20" s="8"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="19410" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21900" windowHeight="9945"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -19,252 +19,282 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="82">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+  <x:si>
+    <x:t xml:space="preserve">RandomItemBox의 파라미터는 획득할수 있는 아이템id 리스트 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItemBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
   <x:si>
     <x:t>허름한 나무 지팡이다.</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Potion_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Armor_3</x:t>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
   </x:si>
   <x:si>
     <x:t>금 갑옷</x:t>
   </x:si>
   <x:si>
+    <x:t>은 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
     <x:t>동 갑옷</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Weapon_1</x:t>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고목 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>떡갈나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법학교에서 본것같은 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_greenSnake_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Apple_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Weapon_3</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Weapon_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Apple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고목 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법학교에서 본것같은 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+    <x:t>Icon/Icon_Item_Weapon_2</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Potion_3</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Apple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>떡갈나무 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨간 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rare</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Potion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_2</x:t>
+    <x:t>UseItemParameterList</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -398,7 +428,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="16">
+  <x:cellXfs count="17">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
@@ -445,6 +475,9 @@
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -1061,85 +1094,102 @@
     <x:col min="5" max="5" width="12.5703125" style="2"/>
     <x:col min="6" max="7" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <x:col min="9" max="16384" width="12.5703125" style="2"/>
+    <x:col min="9" max="9" width="22.5703125" style="2" customWidth="1"/>
+    <x:col min="10" max="10" width="52.85546875" style="2" customWidth="1"/>
+    <x:col min="11" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:10" ht="99" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:8" ht="13.199999999999999">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="J1" s="16" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:10" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>39</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D3" s="14" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>42</x:v>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I3" s="12" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="J3" s="12" t="s">
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>9</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F4" s="4">
         <x:v>20</x:v>
@@ -1148,29 +1198,33 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="4" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I4" s="4" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="J4" s="4" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
       <x:c r="L4" s="4"/>
       <x:c r="M4" s="4"/>
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>38</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>22</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>45</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F5" s="4">
         <x:v>1000</x:v>
@@ -1179,7 +1233,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1189,19 +1243,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>10</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F6" s="4">
         <x:v>0</x:v>
@@ -1210,28 +1264,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="I6" s="4"/>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I6" s="4" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="J6" s="2">
+        <x:v>700</x:v>
+      </x:c>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
       <x:c r="M6" s="4"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="3" t="s">
-        <x:v>40</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F7" s="4">
         <x:v>100</x:v>
@@ -1240,29 +1299,33 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I7" s="4" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="J7" s="4">
+        <x:v>20</x:v>
+      </x:c>
       <x:c r="K7" s="4"/>
       <x:c r="L7" s="4"/>
       <x:c r="M7" s="4"/>
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F8" s="4">
         <x:v>20</x:v>
@@ -1271,29 +1334,33 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="I8" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="J8" s="4" t="s">
+        <x:v>70</x:v>
+      </x:c>
       <x:c r="K8" s="4"/>
       <x:c r="L8" s="4"/>
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B9" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F9" s="4">
         <x:v>50</x:v>
@@ -1302,7 +1369,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H9" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1312,19 +1379,19 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F10" s="4">
         <x:v>50</x:v>
@@ -1333,7 +1400,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H10" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1343,19 +1410,19 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F11" s="4">
         <x:v>10</x:v>
@@ -1364,7 +1431,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -1374,19 +1441,19 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F12" s="4">
         <x:v>10</x:v>
@@ -1395,7 +1462,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -1405,19 +1472,19 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="3" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B13" s="3" t="s">
-        <x:v>3</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F13" s="4">
         <x:v>10</x:v>
@@ -1426,7 +1493,7 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -1436,19 +1503,19 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F14" s="4">
         <x:v>100</x:v>
@@ -1457,7 +1524,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -1467,19 +1534,19 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F15" s="4">
         <x:v>100</x:v>
@@ -1488,7 +1555,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
@@ -1498,19 +1565,19 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>49</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="2">
         <x:v>100</x:v>
@@ -1519,24 +1586,24 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H16" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>0</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="2">
         <x:v>10</x:v>
@@ -1545,24 +1612,24 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>66</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="2">
         <x:v>10</x:v>
@@ -1571,24 +1638,24 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H18" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="8" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>46</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F19" s="2">
         <x:v>10</x:v>
@@ -1597,7 +1664,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H19" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21900" windowHeight="9945"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25875" windowHeight="11475"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -24,284 +24,284 @@
     <x:t xml:space="preserve">RandomItemBox의 파라미터는 획득할수 있는 아이템id 리스트 </x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
     <x:t>화폐</x:t>
   </x:si>
   <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>떡갈나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고목 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법학교에서 본것같은 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_greenSnake_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot_1</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Apple_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Carrot_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
+    <x:t>Item_Potion_3</x:t>
   </x:si>
   <x:si>
     <x:t>RandomItemBox</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
     <x:t>SummonMonster</x:t>
   </x:si>
   <x:si>
     <x:t>Item_DummyBox_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_3</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Armor_2</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Potion_2</x:t>
   </x:si>
   <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허름한 나무 지팡이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Item_Weapon_1</x:t>
   </x:si>
   <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허름한 나무 지팡이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_3</x:t>
-  </x:si>
-  <x:si>
     <x:t>Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨간 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Potion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rare</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고목 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>떡갈나무 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법학교에서 본것같은 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_greenSnake_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Apple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
   </x:si>
 </x:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="7">
     <x:font>
       <x:name val="Arial"/>
       <x:sz val="10"/>
@@ -333,12 +333,7 @@
       <x:color rgb="ff000000"/>
     </x:font>
     <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
-      <x:sz val="10"/>
-      <x:color rgb="ff000000"/>
-    </x:font>
-    <x:font>
-      <x:name val="&quot;맑은 고딕&quot;"/>
+      <x:name val="Arial"/>
       <x:sz val="11"/>
       <x:color rgb="ff008000"/>
     </x:font>
@@ -359,12 +354,6 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffffffff"/>
-        <x:bgColor rgb="ff4d93d9"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffffffff"/>
         <x:bgColor rgb="ffffc000"/>
       </x:patternFill>
     </x:fill>
@@ -376,14 +365,20 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="ffd2f2db"/>
-        <x:bgColor rgb="ffc6efce"/>
+        <x:fgColor rgb="ffffffff"/>
+        <x:bgColor rgb="ff4d93d9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="ffd2f2db"/>
         <x:bgColor indexed="64"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="ffd2f2db"/>
+        <x:bgColor rgb="ffc6efce"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -428,29 +423,17 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:alignment horizontal="general" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="left" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -459,25 +442,28 @@
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="general" vertical="bottom"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="bottom"/>
     </x:xf>
   </x:cellXfs>
@@ -1084,500 +1070,512 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:M35"/>
+  <x:dimension ref="A1:M49"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
-    <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
-    <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
-    <x:col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
-    <x:col min="5" max="5" width="12.5703125" style="2"/>
-    <x:col min="6" max="7" width="12.5703125" style="2" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
-    <x:col min="9" max="9" width="22.5703125" style="2" customWidth="1"/>
-    <x:col min="10" max="10" width="52.85546875" style="2" customWidth="1"/>
-    <x:col min="11" max="16384" width="12.5703125" style="2"/>
+    <x:col min="1" max="1" width="19.42578125" style="1" customWidth="1"/>
+    <x:col min="2" max="2" width="19.5703125" style="1" customWidth="1"/>
+    <x:col min="3" max="3" width="50.7109375" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
+    <x:col min="5" max="5" width="12.5703125" style="1"/>
+    <x:col min="6" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="8" width="28.42578125" style="1" customWidth="1"/>
+    <x:col min="9" max="9" width="22.5703125" style="1" customWidth="1"/>
+    <x:col min="10" max="10" width="52.85546875" style="1" customWidth="1"/>
+    <x:col min="11" max="16384" width="12.5703125" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:10" ht="99" customHeight="1">
-      <x:c r="A1" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="B1" s="1"/>
-      <x:c r="C1" s="1" t="s">
+    <x:row r="1" spans="1:12" ht="99" customHeight="1">
+      <x:c r="A1" s="8" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B1" s="8"/>
+      <x:c r="C1" s="8" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D1" s="2"/>
+      <x:c r="E1" s="2"/>
+      <x:c r="F1" s="2"/>
+      <x:c r="G1" s="2"/>
+      <x:c r="H1" s="2"/>
+      <x:c r="I1" s="2"/>
+      <x:c r="J1" s="8" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K1" s="2"/>
+      <x:c r="L1" s="2"/>
+    </x:row>
+    <x:row r="2" spans="1:12" ht="13.199999999999999">
+      <x:c r="A2" s="8" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C2" s="8" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D2" s="8" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="E2" s="8" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="F2" s="8" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G2" s="8" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="H2" s="8" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I2" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="J2" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="K2" s="2"/>
+      <x:c r="L2" s="2"/>
+    </x:row>
+    <x:row r="3" spans="1:12" s="6" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="A3" s="9" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F3" s="7" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G3" s="7" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H3" s="7" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="J3" s="7" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K3" s="7"/>
+      <x:c r="L3" s="7"/>
+    </x:row>
+    <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A4" s="10" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D4" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E4" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F4" s="2">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="J1" s="16" t="s">
+      <x:c r="G4" s="2">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H4" s="2" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I4" s="2" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="J4" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="K4" s="2"/>
+      <x:c r="L4" s="2"/>
+      <x:c r="M4" s="2"/>
+    </x:row>
+    <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A5" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D5" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E5" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F5" s="2">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="G5" s="2">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="H5" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I5" s="2"/>
+      <x:c r="J5" s="2"/>
+      <x:c r="K5" s="2"/>
+      <x:c r="L5" s="2"/>
+      <x:c r="M5" s="2"/>
+    </x:row>
+    <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A6" s="11" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D6" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E6" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F6" s="2">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:10" ht="13.199999999999999">
-      <x:c r="A2" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="B2" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C2" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:10" s="12" customFormat="1" ht="15.75" customHeight="1">
-      <x:c r="A3" s="11" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D3" s="14" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="I3" s="12" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="J3" s="12" t="s">
-        <x:v>91</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A4" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="B4" s="3" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F4" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G4" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="H4" s="4" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I4" s="4" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="J4" s="4" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="K4" s="4"/>
-      <x:c r="L4" s="4"/>
-      <x:c r="M4" s="4"/>
-    </x:row>
-    <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A5" s="3" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="B5" s="5" t="s">
+      <x:c r="G6" s="2">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C5" s="5" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D5" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E5" s="4" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="F5" s="4">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="G5" s="4">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="H5" s="4" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="I5" s="4"/>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
-      <x:c r="L5" s="4"/>
-      <x:c r="M5" s="4"/>
-    </x:row>
-    <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A6" s="5" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="B6" s="5" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E6" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F6" s="4">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="4">
+      <x:c r="H6" s="2" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="H6" s="4" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="I6" s="4" t="s">
-        <x:v>12</x:v>
+      <x:c r="I6" s="2" t="s">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="J6" s="2">
         <x:v>700</x:v>
       </x:c>
-      <x:c r="K6" s="4"/>
-      <x:c r="L6" s="4"/>
-      <x:c r="M6" s="4"/>
+      <x:c r="K6" s="2"/>
+      <x:c r="L6" s="2"/>
+      <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A7" s="3" t="s">
+      <x:c r="A7" s="10" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B7" s="10" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D7" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F7" s="2">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G7" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H7" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I7" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="J7" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="K7" s="2"/>
+      <x:c r="L7" s="2"/>
+      <x:c r="M7" s="2"/>
+    </x:row>
+    <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A8" s="12" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B8" s="10" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="C8" s="10" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D8" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F8" s="2">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G8" s="2">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H8" s="2" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I8" s="2" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="J8" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="K8" s="2"/>
+      <x:c r="L8" s="2"/>
+      <x:c r="M8" s="2"/>
+    </x:row>
+    <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A9" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B9" s="13" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C9" s="13" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D9" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F9" s="2">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G9" s="2">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H9" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="I9" s="2"/>
+      <x:c r="J9" s="2"/>
+      <x:c r="K9" s="2"/>
+      <x:c r="L9" s="2"/>
+      <x:c r="M9" s="2"/>
+    </x:row>
+    <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A10" s="8" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B10" s="8" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C10" s="8" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D10" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F10" s="2">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G10" s="2">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H10" s="2" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="I10" s="2"/>
+      <x:c r="J10" s="2"/>
+      <x:c r="K10" s="2"/>
+      <x:c r="L10" s="2"/>
+      <x:c r="M10" s="2"/>
+    </x:row>
+    <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A11" s="8" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B11" s="8" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C11" s="8" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D11" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F11" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G11" s="2">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H11" s="2" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="I11" s="2"/>
+      <x:c r="J11" s="2"/>
+      <x:c r="K11" s="2"/>
+      <x:c r="L11" s="2"/>
+      <x:c r="M11" s="2"/>
+    </x:row>
+    <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A12" s="13" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B12" s="13" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="13" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="D12" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="F12" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G12" s="2">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="H12" s="2" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="B7" s="3" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C7" s="3" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="D7" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E7" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F7" s="4">
+      <x:c r="I12" s="2"/>
+      <x:c r="J12" s="2"/>
+      <x:c r="K12" s="2"/>
+      <x:c r="L12" s="2"/>
+      <x:c r="M12" s="2"/>
+    </x:row>
+    <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A13" s="10" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="B13" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C13" s="10" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D13" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F13" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G13" s="2">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="H13" s="2" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="I13" s="2"/>
+      <x:c r="J13" s="2"/>
+      <x:c r="K13" s="2"/>
+      <x:c r="L13" s="2"/>
+      <x:c r="M13" s="2"/>
+    </x:row>
+    <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A14" s="8" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E14" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F14" s="2">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="G7" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H7" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="I7" s="4" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="J7" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="K7" s="4"/>
-      <x:c r="L7" s="4"/>
-      <x:c r="M7" s="4"/>
-    </x:row>
-    <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A8" s="15" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F8" s="4">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G8" s="4">
+      <x:c r="G14" s="2">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="H14" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I14" s="2"/>
+      <x:c r="J14" s="2"/>
+      <x:c r="K14" s="2"/>
+      <x:c r="L14" s="2"/>
+      <x:c r="M14" s="2"/>
+    </x:row>
+    <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
+      <x:c r="A15" s="8" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="B15" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C15" s="8" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D15" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="E15" s="2" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F15" s="2">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="H8" s="4" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="I8" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="J8" s="4" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="K8" s="4"/>
-      <x:c r="L8" s="4"/>
-      <x:c r="M8" s="4"/>
-    </x:row>
-    <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F9" s="4">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G9" s="4">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H9" s="4" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="I9" s="4"/>
-      <x:c r="J9" s="4"/>
-      <x:c r="K9" s="4"/>
-      <x:c r="L9" s="4"/>
-      <x:c r="M9" s="4"/>
-    </x:row>
-    <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A10" s="1" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F10" s="4">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="G10" s="4">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="H10" s="4" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="I10" s="4"/>
-      <x:c r="J10" s="4"/>
-      <x:c r="K10" s="4"/>
-      <x:c r="L10" s="4"/>
-      <x:c r="M10" s="4"/>
-    </x:row>
-    <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A11" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="G15" s="2">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="H15" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="I15" s="2"/>
+      <x:c r="J15" s="2"/>
+      <x:c r="K15" s="2"/>
+      <x:c r="L15" s="2"/>
+      <x:c r="M15" s="2"/>
+    </x:row>
+    <x:row r="16" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A16" s="8" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="B16" s="3" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="3" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="D11" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E11" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F11" s="4">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G11" s="4">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="H11" s="4" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-      <x:c r="L11" s="4"/>
-      <x:c r="M11" s="4"/>
-    </x:row>
-    <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="B12" s="6" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="6" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D12" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E12" s="4" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F12" s="4">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G12" s="4">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="H12" s="4" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-      <x:c r="L12" s="4"/>
-      <x:c r="M12" s="4"/>
-    </x:row>
-    <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A13" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B13" s="3" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="E13" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="F13" s="4">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G13" s="4">
-        <x:v>450</x:v>
-      </x:c>
-      <x:c r="H13" s="4" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-      <x:c r="L13" s="4"/>
-      <x:c r="M13" s="4"/>
-    </x:row>
-    <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E14" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F14" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G14" s="4">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="H14" s="4" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-      <x:c r="L14" s="4"/>
-      <x:c r="M14" s="4"/>
-    </x:row>
-    <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A15" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F15" s="4">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="G15" s="4">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="H15" s="4" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-      <x:c r="L15" s="4"/>
-      <x:c r="M15" s="4"/>
-    </x:row>
-    <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A16" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B16" s="7" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="C16" s="7" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F16" s="2">
         <x:v>100</x:v>
@@ -1586,24 +1584,28 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H16" s="2" t="s">
-        <x:v>88</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A17" s="8" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="B17" s="8" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I16" s="2"/>
+      <x:c r="J16" s="2"/>
+      <x:c r="K16" s="2"/>
+      <x:c r="L16" s="2"/>
+    </x:row>
+    <x:row r="17" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A17" s="3" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B17" s="3" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C17" s="3" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C17" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D17" s="2" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F17" s="2">
         <x:v>10</x:v>
@@ -1612,24 +1614,28 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>83</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A18" s="8" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B18" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C18" s="8" t="s">
-        <x:v>69</x:v>
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I17" s="2"/>
+      <x:c r="J17" s="2"/>
+      <x:c r="K17" s="2"/>
+      <x:c r="L17" s="2"/>
+    </x:row>
+    <x:row r="18" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A18" s="3" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="s">
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F18" s="2">
         <x:v>10</x:v>
@@ -1638,24 +1644,28 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H18" s="2" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <x:c r="A19" s="8" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="B19" s="8" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="C19" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I18" s="2"/>
+      <x:c r="J18" s="2"/>
+      <x:c r="K18" s="2"/>
+      <x:c r="L18" s="2"/>
+    </x:row>
+    <x:row r="19" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A19" s="3" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="s">
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F19" s="2">
         <x:v>10</x:v>
@@ -1664,103 +1674,433 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H19" s="2" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="8"/>
-      <x:c r="B20" s="8"/>
-      <x:c r="C20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="8"/>
-      <x:c r="B21" s="8"/>
-      <x:c r="C21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="8"/>
-      <x:c r="B22" s="8"/>
-      <x:c r="C22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="8"/>
-      <x:c r="B23" s="8"/>
-      <x:c r="C23" s="8"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="8"/>
-      <x:c r="B24" s="8"/>
-      <x:c r="C24" s="8"/>
-    </x:row>
-    <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A25" s="8"/>
-      <x:c r="B25" s="8"/>
-      <x:c r="C25" s="8"/>
-    </x:row>
-    <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="9"/>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
-    </x:row>
-    <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A27" s="9"/>
-      <x:c r="B27" s="9"/>
-      <x:c r="C27" s="9"/>
-    </x:row>
-    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="9"/>
-      <x:c r="B28" s="9"/>
-      <x:c r="C28" s="9"/>
-    </x:row>
-    <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="9"/>
-      <x:c r="B29" s="9"/>
-      <x:c r="C29" s="9"/>
-    </x:row>
-    <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="9"/>
-      <x:c r="B30" s="9"/>
-      <x:c r="C30" s="9"/>
-    </x:row>
-    <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="9"/>
-      <x:c r="B31" s="9"/>
-      <x:c r="C31" s="9"/>
-    </x:row>
-    <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="10"/>
-      <x:c r="B32" s="10"/>
-      <x:c r="C32" s="10"/>
-    </x:row>
-    <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="10"/>
-      <x:c r="B33" s="10"/>
-      <x:c r="C33" s="10"/>
-    </x:row>
-    <x:row r="34" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A34" s="10"/>
-      <x:c r="B34" s="10"/>
-      <x:c r="C34" s="10"/>
-    </x:row>
-    <x:row r="35" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A35" s="10"/>
-      <x:c r="B35" s="10"/>
-      <x:c r="C35" s="10"/>
-    </x:row>
-    <x:row r="36" ht="15.75" customHeight="1"/>
-    <x:row r="37" ht="15.75" customHeight="1"/>
-    <x:row r="38" ht="15.75" customHeight="1"/>
-    <x:row r="39" ht="15.75" customHeight="1"/>
-    <x:row r="40" ht="15.75" customHeight="1"/>
-    <x:row r="41" ht="15.75" customHeight="1"/>
-    <x:row r="42" ht="15.75" customHeight="1"/>
-    <x:row r="43" ht="15.75" customHeight="1"/>
-    <x:row r="44" ht="15.75" customHeight="1"/>
-    <x:row r="45" ht="15.75" customHeight="1"/>
-    <x:row r="46" ht="15.75" customHeight="1"/>
-    <x:row r="47" ht="15.75" customHeight="1"/>
-    <x:row r="48" ht="15.75" customHeight="1"/>
-    <x:row r="49" ht="15.75" customHeight="1"/>
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="I19" s="2"/>
+      <x:c r="J19" s="2"/>
+      <x:c r="K19" s="2"/>
+      <x:c r="L19" s="2"/>
+    </x:row>
+    <x:row r="20" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A20" s="3"/>
+      <x:c r="B20" s="3"/>
+      <x:c r="C20" s="3"/>
+      <x:c r="D20" s="2"/>
+      <x:c r="E20" s="2"/>
+      <x:c r="F20" s="2"/>
+      <x:c r="G20" s="2"/>
+      <x:c r="H20" s="2"/>
+      <x:c r="I20" s="2"/>
+      <x:c r="J20" s="2"/>
+      <x:c r="K20" s="2"/>
+      <x:c r="L20" s="2"/>
+    </x:row>
+    <x:row r="21" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A21" s="3"/>
+      <x:c r="B21" s="3"/>
+      <x:c r="C21" s="3"/>
+      <x:c r="D21" s="2"/>
+      <x:c r="E21" s="2"/>
+      <x:c r="F21" s="2"/>
+      <x:c r="G21" s="2"/>
+      <x:c r="H21" s="2"/>
+      <x:c r="I21" s="2"/>
+      <x:c r="J21" s="2"/>
+      <x:c r="K21" s="2"/>
+      <x:c r="L21" s="2"/>
+    </x:row>
+    <x:row r="22" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A22" s="3"/>
+      <x:c r="B22" s="3"/>
+      <x:c r="C22" s="3"/>
+      <x:c r="D22" s="2"/>
+      <x:c r="E22" s="2"/>
+      <x:c r="F22" s="2"/>
+      <x:c r="G22" s="2"/>
+      <x:c r="H22" s="2"/>
+      <x:c r="I22" s="2"/>
+      <x:c r="J22" s="2"/>
+      <x:c r="K22" s="2"/>
+      <x:c r="L22" s="2"/>
+    </x:row>
+    <x:row r="23" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A23" s="3"/>
+      <x:c r="B23" s="3"/>
+      <x:c r="C23" s="3"/>
+      <x:c r="D23" s="2"/>
+      <x:c r="E23" s="2"/>
+      <x:c r="F23" s="2"/>
+      <x:c r="G23" s="2"/>
+      <x:c r="H23" s="2"/>
+      <x:c r="I23" s="2"/>
+      <x:c r="J23" s="2"/>
+      <x:c r="K23" s="2"/>
+      <x:c r="L23" s="2"/>
+    </x:row>
+    <x:row r="24" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A24" s="3"/>
+      <x:c r="B24" s="3"/>
+      <x:c r="C24" s="3"/>
+      <x:c r="D24" s="2"/>
+      <x:c r="E24" s="2"/>
+      <x:c r="F24" s="2"/>
+      <x:c r="G24" s="2"/>
+      <x:c r="H24" s="2"/>
+      <x:c r="I24" s="2"/>
+      <x:c r="J24" s="2"/>
+      <x:c r="K24" s="2"/>
+      <x:c r="L24" s="2"/>
+    </x:row>
+    <x:row r="25" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A25" s="3"/>
+      <x:c r="B25" s="3"/>
+      <x:c r="C25" s="3"/>
+      <x:c r="D25" s="2"/>
+      <x:c r="E25" s="2"/>
+      <x:c r="F25" s="2"/>
+      <x:c r="G25" s="2"/>
+      <x:c r="H25" s="2"/>
+      <x:c r="I25" s="2"/>
+      <x:c r="J25" s="2"/>
+      <x:c r="K25" s="2"/>
+      <x:c r="L25" s="2"/>
+    </x:row>
+    <x:row r="26" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A26" s="4"/>
+      <x:c r="B26" s="4"/>
+      <x:c r="C26" s="4"/>
+      <x:c r="D26" s="2"/>
+      <x:c r="E26" s="2"/>
+      <x:c r="F26" s="2"/>
+      <x:c r="G26" s="2"/>
+      <x:c r="H26" s="2"/>
+      <x:c r="I26" s="2"/>
+      <x:c r="J26" s="2"/>
+      <x:c r="K26" s="2"/>
+      <x:c r="L26" s="2"/>
+    </x:row>
+    <x:row r="27" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A27" s="4"/>
+      <x:c r="B27" s="4"/>
+      <x:c r="C27" s="4"/>
+      <x:c r="D27" s="2"/>
+      <x:c r="E27" s="2"/>
+      <x:c r="F27" s="2"/>
+      <x:c r="G27" s="2"/>
+      <x:c r="H27" s="2"/>
+      <x:c r="I27" s="2"/>
+      <x:c r="J27" s="2"/>
+      <x:c r="K27" s="2"/>
+      <x:c r="L27" s="2"/>
+    </x:row>
+    <x:row r="28" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="2"/>
+      <x:c r="E28" s="2"/>
+      <x:c r="F28" s="2"/>
+      <x:c r="G28" s="2"/>
+      <x:c r="H28" s="2"/>
+      <x:c r="I28" s="2"/>
+      <x:c r="J28" s="2"/>
+      <x:c r="K28" s="2"/>
+      <x:c r="L28" s="2"/>
+    </x:row>
+    <x:row r="29" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="2"/>
+      <x:c r="E29" s="2"/>
+      <x:c r="F29" s="2"/>
+      <x:c r="G29" s="2"/>
+      <x:c r="H29" s="2"/>
+      <x:c r="I29" s="2"/>
+      <x:c r="J29" s="2"/>
+      <x:c r="K29" s="2"/>
+      <x:c r="L29" s="2"/>
+    </x:row>
+    <x:row r="30" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A30" s="4"/>
+      <x:c r="B30" s="4"/>
+      <x:c r="C30" s="4"/>
+      <x:c r="D30" s="2"/>
+      <x:c r="E30" s="2"/>
+      <x:c r="F30" s="2"/>
+      <x:c r="G30" s="2"/>
+      <x:c r="H30" s="2"/>
+      <x:c r="I30" s="2"/>
+      <x:c r="J30" s="2"/>
+      <x:c r="K30" s="2"/>
+      <x:c r="L30" s="2"/>
+    </x:row>
+    <x:row r="31" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A31" s="4"/>
+      <x:c r="B31" s="4"/>
+      <x:c r="C31" s="4"/>
+      <x:c r="D31" s="2"/>
+      <x:c r="E31" s="2"/>
+      <x:c r="F31" s="2"/>
+      <x:c r="G31" s="2"/>
+      <x:c r="H31" s="2"/>
+      <x:c r="I31" s="2"/>
+      <x:c r="J31" s="2"/>
+      <x:c r="K31" s="2"/>
+      <x:c r="L31" s="2"/>
+    </x:row>
+    <x:row r="32" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A32" s="5"/>
+      <x:c r="B32" s="5"/>
+      <x:c r="C32" s="5"/>
+      <x:c r="D32" s="2"/>
+      <x:c r="E32" s="2"/>
+      <x:c r="F32" s="2"/>
+      <x:c r="G32" s="2"/>
+      <x:c r="H32" s="2"/>
+      <x:c r="I32" s="2"/>
+      <x:c r="J32" s="2"/>
+      <x:c r="K32" s="2"/>
+      <x:c r="L32" s="2"/>
+    </x:row>
+    <x:row r="33" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A33" s="5"/>
+      <x:c r="B33" s="5"/>
+      <x:c r="C33" s="5"/>
+      <x:c r="D33" s="2"/>
+      <x:c r="E33" s="2"/>
+      <x:c r="F33" s="2"/>
+      <x:c r="G33" s="2"/>
+      <x:c r="H33" s="2"/>
+      <x:c r="I33" s="2"/>
+      <x:c r="J33" s="2"/>
+      <x:c r="K33" s="2"/>
+      <x:c r="L33" s="2"/>
+    </x:row>
+    <x:row r="34" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A34" s="5"/>
+      <x:c r="B34" s="5"/>
+      <x:c r="C34" s="5"/>
+      <x:c r="D34" s="2"/>
+      <x:c r="E34" s="2"/>
+      <x:c r="F34" s="2"/>
+      <x:c r="G34" s="2"/>
+      <x:c r="H34" s="2"/>
+      <x:c r="I34" s="2"/>
+      <x:c r="J34" s="2"/>
+      <x:c r="K34" s="2"/>
+      <x:c r="L34" s="2"/>
+    </x:row>
+    <x:row r="35" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A35" s="5"/>
+      <x:c r="B35" s="5"/>
+      <x:c r="C35" s="5"/>
+      <x:c r="D35" s="2"/>
+      <x:c r="E35" s="2"/>
+      <x:c r="F35" s="2"/>
+      <x:c r="G35" s="2"/>
+      <x:c r="H35" s="2"/>
+      <x:c r="I35" s="2"/>
+      <x:c r="J35" s="2"/>
+      <x:c r="K35" s="2"/>
+      <x:c r="L35" s="2"/>
+    </x:row>
+    <x:row r="36" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A36" s="2"/>
+      <x:c r="B36" s="2"/>
+      <x:c r="C36" s="2"/>
+      <x:c r="D36" s="2"/>
+      <x:c r="E36" s="2"/>
+      <x:c r="F36" s="2"/>
+      <x:c r="G36" s="2"/>
+      <x:c r="H36" s="2"/>
+      <x:c r="I36" s="2"/>
+      <x:c r="J36" s="2"/>
+      <x:c r="K36" s="2"/>
+      <x:c r="L36" s="2"/>
+    </x:row>
+    <x:row r="37" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A37" s="2"/>
+      <x:c r="B37" s="2"/>
+      <x:c r="C37" s="2"/>
+      <x:c r="D37" s="2"/>
+      <x:c r="E37" s="2"/>
+      <x:c r="F37" s="2"/>
+      <x:c r="G37" s="2"/>
+      <x:c r="H37" s="2"/>
+      <x:c r="I37" s="2"/>
+      <x:c r="J37" s="2"/>
+      <x:c r="K37" s="2"/>
+      <x:c r="L37" s="2"/>
+    </x:row>
+    <x:row r="38" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A38" s="2"/>
+      <x:c r="B38" s="2"/>
+      <x:c r="C38" s="2"/>
+      <x:c r="D38" s="2"/>
+      <x:c r="E38" s="2"/>
+      <x:c r="F38" s="2"/>
+      <x:c r="G38" s="2"/>
+      <x:c r="H38" s="2"/>
+      <x:c r="I38" s="2"/>
+      <x:c r="J38" s="2"/>
+      <x:c r="K38" s="2"/>
+      <x:c r="L38" s="2"/>
+    </x:row>
+    <x:row r="39" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A39" s="2"/>
+      <x:c r="B39" s="2"/>
+      <x:c r="C39" s="2"/>
+      <x:c r="D39" s="2"/>
+      <x:c r="E39" s="2"/>
+      <x:c r="F39" s="2"/>
+      <x:c r="G39" s="2"/>
+      <x:c r="H39" s="2"/>
+      <x:c r="I39" s="2"/>
+      <x:c r="J39" s="2"/>
+      <x:c r="K39" s="2"/>
+      <x:c r="L39" s="2"/>
+    </x:row>
+    <x:row r="40" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A40" s="2"/>
+      <x:c r="B40" s="2"/>
+      <x:c r="C40" s="2"/>
+      <x:c r="D40" s="2"/>
+      <x:c r="E40" s="2"/>
+      <x:c r="F40" s="2"/>
+      <x:c r="G40" s="2"/>
+      <x:c r="H40" s="2"/>
+      <x:c r="I40" s="2"/>
+      <x:c r="J40" s="2"/>
+      <x:c r="K40" s="2"/>
+      <x:c r="L40" s="2"/>
+    </x:row>
+    <x:row r="41" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A41" s="2"/>
+      <x:c r="B41" s="2"/>
+      <x:c r="C41" s="2"/>
+      <x:c r="D41" s="2"/>
+      <x:c r="E41" s="2"/>
+      <x:c r="F41" s="2"/>
+      <x:c r="G41" s="2"/>
+      <x:c r="H41" s="2"/>
+      <x:c r="I41" s="2"/>
+      <x:c r="J41" s="2"/>
+      <x:c r="K41" s="2"/>
+      <x:c r="L41" s="2"/>
+    </x:row>
+    <x:row r="42" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A42" s="2"/>
+      <x:c r="B42" s="2"/>
+      <x:c r="C42" s="2"/>
+      <x:c r="D42" s="2"/>
+      <x:c r="E42" s="2"/>
+      <x:c r="F42" s="2"/>
+      <x:c r="G42" s="2"/>
+      <x:c r="H42" s="2"/>
+      <x:c r="I42" s="2"/>
+      <x:c r="J42" s="2"/>
+      <x:c r="K42" s="2"/>
+      <x:c r="L42" s="2"/>
+    </x:row>
+    <x:row r="43" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A43" s="2"/>
+      <x:c r="B43" s="2"/>
+      <x:c r="C43" s="2"/>
+      <x:c r="D43" s="2"/>
+      <x:c r="E43" s="2"/>
+      <x:c r="F43" s="2"/>
+      <x:c r="G43" s="2"/>
+      <x:c r="H43" s="2"/>
+      <x:c r="I43" s="2"/>
+      <x:c r="J43" s="2"/>
+      <x:c r="K43" s="2"/>
+      <x:c r="L43" s="2"/>
+    </x:row>
+    <x:row r="44" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A44" s="2"/>
+      <x:c r="B44" s="2"/>
+      <x:c r="C44" s="2"/>
+      <x:c r="D44" s="2"/>
+      <x:c r="E44" s="2"/>
+      <x:c r="F44" s="2"/>
+      <x:c r="G44" s="2"/>
+      <x:c r="H44" s="2"/>
+      <x:c r="I44" s="2"/>
+      <x:c r="J44" s="2"/>
+      <x:c r="K44" s="2"/>
+      <x:c r="L44" s="2"/>
+    </x:row>
+    <x:row r="45" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A45" s="2"/>
+      <x:c r="B45" s="2"/>
+      <x:c r="C45" s="2"/>
+      <x:c r="D45" s="2"/>
+      <x:c r="E45" s="2"/>
+      <x:c r="F45" s="2"/>
+      <x:c r="G45" s="2"/>
+      <x:c r="H45" s="2"/>
+      <x:c r="I45" s="2"/>
+      <x:c r="J45" s="2"/>
+      <x:c r="K45" s="2"/>
+      <x:c r="L45" s="2"/>
+    </x:row>
+    <x:row r="46" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A46" s="2"/>
+      <x:c r="B46" s="2"/>
+      <x:c r="C46" s="2"/>
+      <x:c r="D46" s="2"/>
+      <x:c r="E46" s="2"/>
+      <x:c r="F46" s="2"/>
+      <x:c r="G46" s="2"/>
+      <x:c r="H46" s="2"/>
+      <x:c r="I46" s="2"/>
+      <x:c r="J46" s="2"/>
+      <x:c r="K46" s="2"/>
+      <x:c r="L46" s="2"/>
+    </x:row>
+    <x:row r="47" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A47" s="2"/>
+      <x:c r="B47" s="2"/>
+      <x:c r="C47" s="2"/>
+      <x:c r="D47" s="2"/>
+      <x:c r="E47" s="2"/>
+      <x:c r="F47" s="2"/>
+      <x:c r="G47" s="2"/>
+      <x:c r="H47" s="2"/>
+      <x:c r="I47" s="2"/>
+      <x:c r="J47" s="2"/>
+      <x:c r="K47" s="2"/>
+      <x:c r="L47" s="2"/>
+    </x:row>
+    <x:row r="48" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A48" s="2"/>
+      <x:c r="B48" s="2"/>
+      <x:c r="C48" s="2"/>
+      <x:c r="D48" s="2"/>
+      <x:c r="E48" s="2"/>
+      <x:c r="F48" s="2"/>
+      <x:c r="G48" s="2"/>
+      <x:c r="H48" s="2"/>
+      <x:c r="I48" s="2"/>
+      <x:c r="J48" s="2"/>
+      <x:c r="K48" s="2"/>
+      <x:c r="L48" s="2"/>
+    </x:row>
+    <x:row r="49" spans="1:12" ht="15.75" customHeight="1">
+      <x:c r="A49" s="2"/>
+      <x:c r="B49" s="2"/>
+      <x:c r="C49" s="2"/>
+      <x:c r="D49" s="2"/>
+      <x:c r="E49" s="2"/>
+      <x:c r="F49" s="2"/>
+      <x:c r="G49" s="2"/>
+      <x:c r="H49" s="2"/>
+      <x:c r="I49" s="2"/>
+      <x:c r="J49" s="2"/>
+      <x:c r="K49" s="2"/>
+      <x:c r="L49" s="2"/>
+    </x:row>
     <x:row r="50" ht="15.75" customHeight="1"/>
     <x:row r="51" ht="15.75" customHeight="1"/>
     <x:row r="52" ht="15.75" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25875" windowHeight="11475"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="21720" windowHeight="11490"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,280 +21,280 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <x:si>
+    <x:t>나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Normal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고목 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RandomItemBox</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeHp</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SummonMonster</x:t>
+  </x:si>
+  <x:si>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허름한 나무 지팡이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>떡갈나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemParameterList</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Box_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
     <x:t xml:space="preserve">RandomItemBox의 파라미터는 획득할수 있는 아이템id 리스트 </x:t>
   </x:si>
   <x:si>
+    <x:t>mob_greenSnake_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법학교에서 본것같은 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
   </x:si>
   <x:si>
+    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
+  </x:si>
+  <x:si>
     <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>떡갈나무 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>나무 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨간 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Potion</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Rare</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고목 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법학교에서 본것같은 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_greenSnake_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Box_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Apple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemParameterList</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>StatChangeHp</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Apple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RandomItemBox</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SummonMonster</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허름한 나무 지팡이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1087,11 +1087,11 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="99" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8" t="s">
-        <x:v>74</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1100,94 +1100,94 @@
       <x:c r="H1" s="2"/>
       <x:c r="I1" s="2"/>
       <x:c r="J1" s="8" t="s">
-        <x:v>0</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="K1" s="2"/>
       <x:c r="L1" s="2"/>
     </x:row>
     <x:row r="2" spans="1:12" ht="13.199999999999999">
       <x:c r="A2" s="8" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B2" s="8" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="B2" s="8" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="C2" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D2" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E2" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F2" s="8" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="G2" s="8" t="s">
-        <x:v>13</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="H2" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:12" s="6" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="9" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B3" s="9" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C3" s="9" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D3" s="7" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="E3" s="7" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="B3" s="9" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="C3" s="9" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D3" s="7" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="E3" s="7" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>73</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>85</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I3" s="7" t="s">
-        <x:v>16</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K3" s="7"/>
       <x:c r="L3" s="7"/>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="10" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="B4" s="10" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C4" s="10" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="B4" s="10" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C4" s="10" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>20</x:v>
@@ -1196,13 +1196,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I4" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J4" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="K4" s="2"/>
       <x:c r="L4" s="2"/>
@@ -1210,19 +1210,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B5" s="11" t="s">
-        <x:v>5</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1000</x:v>
@@ -1231,7 +1231,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="I5" s="2"/>
       <x:c r="J5" s="2"/>
@@ -1241,19 +1241,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="11" t="s">
-        <x:v>40</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B6" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>86</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E6" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F6" s="2">
         <x:v>0</x:v>
@@ -1262,10 +1262,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I6" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="J6" s="2">
         <x:v>700</x:v>
@@ -1276,19 +1276,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="10" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C7" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C7" s="10" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F7" s="2">
         <x:v>100</x:v>
@@ -1297,10 +1297,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I7" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J7" s="2">
         <x:v>20</x:v>
@@ -1311,19 +1311,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>75</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="10" t="s">
-        <x:v>4</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="10" t="s">
-        <x:v>45</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F8" s="2">
         <x:v>20</x:v>
@@ -1332,13 +1332,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="I8" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="J8" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K8" s="2"/>
       <x:c r="L8" s="2"/>
@@ -1346,19 +1346,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="13" t="s">
-        <x:v>76</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>2</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F9" s="2">
         <x:v>50</x:v>
@@ -1367,7 +1367,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H9" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>
@@ -1377,19 +1377,19 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B10" s="8" t="s">
-        <x:v>8</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C10" s="8" t="s">
-        <x:v>44</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>50</x:v>
@@ -1398,7 +1398,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H10" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="I10" s="2"/>
       <x:c r="J10" s="2"/>
@@ -1408,19 +1408,19 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="8" t="s">
-        <x:v>89</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B11" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>10</x:v>
@@ -1429,7 +1429,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H11" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I11" s="2"/>
       <x:c r="J11" s="2"/>
@@ -1439,19 +1439,19 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="13" t="s">
-        <x:v>83</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>32</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C12" s="13" t="s">
-        <x:v>3</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>10</x:v>
@@ -1460,7 +1460,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H12" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="I12" s="2"/>
       <x:c r="J12" s="2"/>
@@ -1470,19 +1470,19 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="10" t="s">
-        <x:v>80</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B13" s="10" t="s">
-        <x:v>29</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C13" s="10" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>10</x:v>
@@ -1491,7 +1491,7 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="H13" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="I13" s="2"/>
       <x:c r="J13" s="2"/>
@@ -1501,19 +1501,19 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="8" t="s">
-        <x:v>91</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B14" s="8" t="s">
-        <x:v>27</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="8" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D14" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E14" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="2">
         <x:v>100</x:v>
@@ -1522,7 +1522,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H14" s="2" t="s">
-        <x:v>58</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I14" s="2"/>
       <x:c r="J14" s="2"/>
@@ -1532,19 +1532,19 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="8" t="s">
-        <x:v>84</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C15" s="8" t="s">
-        <x:v>53</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F15" s="2">
         <x:v>100</x:v>
@@ -1553,7 +1553,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H15" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="I15" s="2"/>
       <x:c r="J15" s="2"/>
@@ -1563,19 +1563,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A16" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>34</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F16" s="2">
         <x:v>100</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H16" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I16" s="2"/>
       <x:c r="J16" s="2"/>
@@ -1593,19 +1593,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A17" s="3" t="s">
-        <x:v>90</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>26</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>87</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F17" s="2">
         <x:v>10</x:v>
@@ -1614,7 +1614,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>56</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="I17" s="2"/>
       <x:c r="J17" s="2"/>
@@ -1623,19 +1623,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A18" s="3" t="s">
-        <x:v>72</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B18" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C18" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F18" s="2">
         <x:v>10</x:v>
@@ -1644,7 +1644,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H18" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="I18" s="2"/>
       <x:c r="J18" s="2"/>
@@ -1653,19 +1653,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A19" s="3" t="s">
-        <x:v>88</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B19" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F19" s="2">
         <x:v>10</x:v>
@@ -1674,7 +1674,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H19" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="I19" s="2"/>
       <x:c r="J19" s="2"/>

--- a/JsonConverter/ExcelFiles/DNItem.xlsx
+++ b/JsonConverter/ExcelFiles/DNItem.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="21720" windowHeight="11490"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20925" windowHeight="11340"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -21,280 +21,280 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_3]</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RandomItemBox의 파라미터는 획득할수 있는 아이템id 리스트 </x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_2]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_1]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_7]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_8]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Corn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mob_greenSnake_1:2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마법학교에서 본것같은 지팡이.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>int</x:t>
+  </x:si>
+  <x:si>
+    <x:t>감자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수</x:t>
+  </x:si>
+  <x:si>
+    <x:t>사과</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화폐</x:t>
+  </x:si>
+  <x:si>
+    <x:t>당근</x:t>
+  </x:si>
+  <x:si>
+    <x:t>상자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_0]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>의문의 모자</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Legend</x:t>
+  </x:si>
+  <x:si>
+    <x:t>옥수수다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Potion</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
     <x:t>나무 지팡이</x:t>
   </x:si>
   <x:si>
-    <x:t>Potion</x:t>
+    <x:t>동 갑옷</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고목 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>빨간 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Weapon</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황 포션</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
   </x:si>
   <x:si>
     <x:t>은 갑옷</x:t>
   </x:si>
   <x:si>
-    <x:t>의문의 모자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Legend</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동 갑옷</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Weapon</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Epic</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수다</x:t>
-  </x:si>
-  <x:si>
     <x:t>Normal</x:t>
   </x:si>
   <x:si>
     <x:t>Rare</x:t>
   </x:si>
   <x:si>
-    <x:t>고목 지팡이</x:t>
-  </x:si>
-  <x:si>
     <x:t>금 갑옷</x:t>
   </x:si>
   <x:si>
-    <x:t>Grade</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>빨간 포션</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화폐</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자</x:t>
-  </x:si>
-  <x:si>
-    <x:t>사과</x:t>
-  </x:si>
-  <x:si>
-    <x:t>당근</x:t>
-  </x:si>
-  <x:si>
-    <x:t>옥수수</x:t>
-  </x:si>
-  <x:si>
-    <x:t>int</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>떡갈나무 지팡이</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string[]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UseItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Corn_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>지역에 나타나는 금화</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Equipment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ItemType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>허름한 나무 지팡이다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_DummyBox_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MaxStackCount</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potato_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Armor_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Weapon_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>착용하면 공격력이 강해진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Potion_3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SellingPrice</x:t>
   </x:si>
   <x:si>
     <x:t>Item_Apple_1</x:t>
   </x:si>
   <x:si>
-    <x:t>MaxStackCount</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potato_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_DummyBox_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>RandomItemBox</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Armor_3</x:t>
+    <x:t>StatChangeAtk</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Item_Carrot_1</x:t>
   </x:si>
   <x:si>
     <x:t>StatChangeHp</x:t>
   </x:si>
   <x:si>
+    <x:t>Item_Armor_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>SummonMonster</x:t>
   </x:si>
   <x:si>
-    <x:t>StatChangeAtk</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Carrot_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SellingPrice</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>허름한 나무 지팡이다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Potion_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Weapon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>착용하면 공격력이 강해진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>Item_Equip_Hat_1:1,Item_Corn_1:20,Item_Gold_1:100</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Equipment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>지역에 나타나는 금화</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Corn_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>떡갈나무 지팡이</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UseItemType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string[]</x:t>
+    <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Gold_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_Item_Apple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
   </x:si>
   <x:si>
     <x:t>UseItemParameterList</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Potion_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_2</x:t>
+    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Icon_Item_Box_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Icon_Item_Weapon_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>붉은색의 물약, 체력을 20 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>금으로 만들어진 갑옷, 일단 비싸보인다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Armor_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Gold_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>하얀색의 물약, 체력을 150 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Weapon_3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Potion_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>주황색의 물약, 체력을 50 회복시킨다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Apple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RandomItemBox의 파라미터는 획득할수 있는 아이템id 리스트 </x:t>
-  </x:si>
-  <x:si>
-    <x:t>mob_greenSnake_1:2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>세월의 흔적이 느껴지는 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>상자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 제출용 당근, 작동하겟지..?</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>동으로 만들어진 갑옷, 싸구려다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>감자다. 딱히 의미가 있진 않다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마법학교에서 본것같은 지팡이.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Corn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Icon_Item_Equip_Hat_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>은으로 만들어진 갑옷, 조금은 실용성이 느껴진다.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>과제 실습용 당근, 이번엔 작동했으면 좋겠다</x:t>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_6]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_4]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Icon_ItemList[Icon_ItemList_5]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1079,7 +1079,7 @@
     <x:col min="4" max="4" width="26.5703125" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="12.5703125" style="1"/>
     <x:col min="6" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="8" max="8" width="28.42578125" style="1" customWidth="1"/>
+    <x:col min="8" max="8" width="35.14453125" style="1" customWidth="1"/>
     <x:col min="9" max="9" width="22.5703125" style="1" customWidth="1"/>
     <x:col min="10" max="10" width="52.85546875" style="1" customWidth="1"/>
     <x:col min="11" max="16384" width="12.5703125" style="1"/>
@@ -1087,11 +1087,11 @@
   <x:sheetData>
     <x:row r="1" spans="1:12" ht="99" customHeight="1">
       <x:c r="A1" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B1" s="8"/>
       <x:c r="C1" s="8" t="s">
-        <x:v>52</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D1" s="2"/>
       <x:c r="E1" s="2"/>
@@ -1100,94 +1100,94 @@
       <x:c r="H1" s="2"/>
       <x:c r="I1" s="2"/>
       <x:c r="J1" s="8" t="s">
-        <x:v>79</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K1" s="2"/>
       <x:c r="L1" s="2"/>
     </x:row>
     <x:row r="2" spans="1:12" ht="13.199999999999999">
       <x:c r="A2" s="8" t="s">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B2" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C2" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D2" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E2" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F2" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G2" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H2" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="I2" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="J2" s="2" t="s">
-        <x:v>61</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="2"/>
       <x:c r="L2" s="2"/>
     </x:row>
     <x:row r="3" spans="1:12" s="6" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="9" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B3" s="9" t="s">
-        <x:v>51</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C3" s="9" t="s">
-        <x:v>46</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D3" s="7" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E3" s="7" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F3" s="7" t="s">
-        <x:v>26</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G3" s="7" t="s">
-        <x:v>38</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H3" s="7" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I3" s="7" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="I3" s="7" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="J3" s="7" t="s">
-        <x:v>62</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="K3" s="7"/>
       <x:c r="L3" s="7"/>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="10" t="s">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B4" s="10" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C4" s="10" t="s">
-        <x:v>82</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D4" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E4" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F4" s="2">
         <x:v>20</x:v>
@@ -1196,13 +1196,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H4" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I4" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="J4" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K4" s="2"/>
       <x:c r="L4" s="2"/>
@@ -1210,19 +1210,19 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="10" t="s">
-        <x:v>55</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B5" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="11" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D5" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E5" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F5" s="2">
         <x:v>1000</x:v>
@@ -1231,7 +1231,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="H5" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="I5" s="2"/>
       <x:c r="J5" s="2"/>
@@ -1241,19 +1241,19 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="11" t="s">
-        <x:v>84</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C6" s="11" t="s">
-        <x:v>45</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D6" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E6" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F6" s="2">
         <x:v>0</x:v>
@@ -1262,10 +1262,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="H6" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I6" s="2" t="s">
-        <x:v>34</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="J6" s="2">
         <x:v>700</x:v>
@@ -1276,19 +1276,19 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="10" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B7" s="10" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="10" t="s">
-        <x:v>9</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E7" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F7" s="2">
         <x:v>100</x:v>
@@ -1297,10 +1297,10 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="H7" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="I7" s="2" t="s">
-        <x:v>32</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="J7" s="2">
         <x:v>20</x:v>
@@ -1311,19 +1311,19 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="12" t="s">
-        <x:v>27</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B8" s="10" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="C8" s="10" t="s">
-        <x:v>86</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D8" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E8" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F8" s="2">
         <x:v>20</x:v>
@@ -1332,13 +1332,13 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H8" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="I8" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="J8" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="K8" s="2"/>
       <x:c r="L8" s="2"/>
@@ -1346,19 +1346,19 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B9" s="13" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C9" s="13" t="s">
-        <x:v>91</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D9" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E9" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F9" s="2">
         <x:v>50</x:v>
@@ -1367,7 +1367,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H9" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="I9" s="2"/>
       <x:c r="J9" s="2"/>
@@ -1377,19 +1377,19 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B10" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D10" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E10" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F10" s="2">
         <x:v>50</x:v>
@@ -1398,7 +1398,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H10" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="I10" s="2"/>
       <x:c r="J10" s="2"/>
@@ -1408,19 +1408,19 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B11" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C11" s="8" t="s">
-        <x:v>85</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D11" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E11" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F11" s="2">
         <x:v>10</x:v>
@@ -1429,7 +1429,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H11" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I11" s="2"/>
       <x:c r="J11" s="2"/>
@@ -1439,19 +1439,19 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="13" t="s">
-        <x:v>36</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B12" s="13" t="s">
-        <x:v>2</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C12" s="13" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D12" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E12" s="2" t="s">
-        <x:v>11</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F12" s="2">
         <x:v>10</x:v>
@@ -1460,7 +1460,7 @@
         <x:v>150</x:v>
       </x:c>
       <x:c r="H12" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I12" s="2"/>
       <x:c r="J12" s="2"/>
@@ -1470,19 +1470,19 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="10" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="10" t="s">
-        <x:v>13</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C13" s="10" t="s">
-        <x:v>70</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D13" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E13" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="2">
         <x:v>10</x:v>
@@ -1491,7 +1491,7 @@
         <x:v>450</x:v>
       </x:c>
       <x:c r="H13" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="I13" s="2"/>
       <x:c r="J13" s="2"/>
@@ -1501,19 +1501,19 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="8" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="B14" s="8" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="8" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D14" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E14" s="2" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="B14" s="8" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C14" s="8" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D14" s="2" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E14" s="2" t="s">
-        <x:v>10</x:v>
       </x:c>
       <x:c r="F14" s="2">
         <x:v>100</x:v>
@@ -1522,7 +1522,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H14" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="I14" s="2"/>
       <x:c r="J14" s="2"/>
@@ -1532,19 +1532,19 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="8" t="s">
-        <x:v>77</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D15" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E15" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F15" s="2">
         <x:v>100</x:v>
@@ -1553,7 +1553,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="H15" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I15" s="2"/>
       <x:c r="J15" s="2"/>
@@ -1563,19 +1563,19 @@
     </x:row>
     <x:row r="16" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A16" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B16" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C16" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F16" s="2">
         <x:v>100</x:v>
@@ -1584,7 +1584,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="H16" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="I16" s="2"/>
       <x:c r="J16" s="2"/>
@@ -1593,19 +1593,19 @@
     </x:row>
     <x:row r="17" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A17" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B17" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C17" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F17" s="2">
         <x:v>10</x:v>
@@ -1614,7 +1614,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="H17" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="I17" s="2"/>
       <x:c r="J17" s="2"/>
@@ -1623,19 +1623,19 @@
     </x:row>
     <x:row r="18" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A18" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B18" s="3" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C18" s="3" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="B18" s="3" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C18" s="3" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D18" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F18" s="2">
         <x:v>10</x:v>
@@ -1644,7 +1644,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H18" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="I18" s="2"/>
       <x:c r="J18" s="2"/>
@@ -1653,19 +1653,19 @@
     </x:row>
     <x:row r="19" spans="1:12" ht="15.75" customHeight="1">
       <x:c r="A19" s="3" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="B19" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C19" s="3" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="B19" s="3" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C19" s="3" t="s">
-        <x:v>87</x:v>
-      </x:c>
-      <x:c r="D19" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E19" s="2" t="s">
-        <x:v>8</x:v>
       </x:c>
       <x:c r="F19" s="2">
         <x:v>10</x:v>
@@ -1674,7 +1674,7 @@
         <x:v>200</x:v>
       </x:c>
       <x:c r="H19" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="I19" s="2"/>
       <x:c r="J19" s="2"/>
